--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -16293,6 +16293,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16441,6 +16446,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16589,6 +16599,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16737,6 +16752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16885,6 +16905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17033,6 +17058,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21897,6 +21927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27806,6 +27841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27954,6 +27994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28102,6 +28147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28250,6 +28300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28398,6 +28453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28546,6 +28606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28694,6 +28759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28842,6 +28912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28990,6 +29065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29138,6 +29218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29284,6 +29369,11 @@
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         </is>
       </c>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AT95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
@@ -29005,17 +29005,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -29040,98 +29040,182 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="P148" t="n">
+        <v>2</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>0</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_DE_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -29158,17 +29242,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BB</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Brandenburg, Germany</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -29193,98 +29277,175 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:DE-BB:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>0</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29311,17 +29472,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29346,96 +29507,3852 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:DE-BE:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>0</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DE-BW</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Baden-Württemberg, Germany</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>2</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:DE-BW:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>DE-BY</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bayern, Germany</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:DE-BY:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>DE-HB</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bremen, Germany</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>2</v>
+      </c>
+      <c r="O153" t="n">
+        <v>2</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:DE-HB:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>DE-HE</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hessen, Germany</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>2</v>
+      </c>
+      <c r="O154" t="n">
+        <v>2</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>DE-HH</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>2</v>
+      </c>
+      <c r="O155" t="n">
+        <v>2</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:DE-HH:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DE-MV</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Mecklenburg-Vorpommern, Germany</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="n">
+        <v>2</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:DE-MV:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DE-NI</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Niedersachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>2</v>
+      </c>
+      <c r="O157" t="n">
+        <v>2</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:DE-NI:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DE-NW</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Nordrhein-Westfalen, Germany</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>2</v>
+      </c>
+      <c r="O158" t="n">
+        <v>2</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:DE-NW:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>DE-RP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Rheinland-Pfalz, Germany</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:DE-RP:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>DE-SH</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Schleswig-Holstein, Germany</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="n">
+        <v>2</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:DE-SH:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>DE-SL</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Saarland, Germany</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:DE-SL:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>DE-SN</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Sachsen, Germany</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:DE-SN:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>DE-ST</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Sachsen-Anhalt, Germany</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:DE-ST:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DE-TH</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Thüringen, Germany</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="n">
+        <v>2</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>virale-h-morrhagische-fieber</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Virale hämorrhagische Fieber</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:DE-TH:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV150" t="inlineStr">
+      <c r="AV165" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AW165" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AX165" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr">
+      <c r="AY165" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ150" t="inlineStr">
+      <c r="AZ165" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
         </is>
       </c>
-      <c r="BA150" t="inlineStr">
+      <c r="BA165" t="inlineStr">
         <is>
           <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr">
+      <c r="BB165" t="inlineStr">
         <is>
           <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
-      <c r="BC150" t="inlineStr">
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>viral-hemorrhagic-fevers</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D127</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Viral hemorrhagic fevers</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>病毒性出血热</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -29567,7 +33484,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -29587,7 +33504,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -29597,7 +33514,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -29242,17 +29242,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>DE-BB</t>
+          <t>DE-BW</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Brandenburg, Germany</t>
+          <t>Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -29286,126 +29286,52 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U149" t="inlineStr">
         <is>
           <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
         </is>
       </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:DE-BB:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL149" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>0</v>
-      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
         <v>1</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -29477,12 +29403,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>DE-BE</t>
+          <t>DE-BW</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29516,10 +29442,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -29563,12 +29489,12 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>country:DE-BE:national</t>
+          <t>country:DE-BW:national</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
         <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE150" t="inlineStr">
@@ -29612,30 +29538,34 @@
         </is>
       </c>
       <c r="AN150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT150" t="n">
         <v>1</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -29702,17 +29632,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>DE-BW</t>
+          <t>DE-RP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Baden-Württemberg, Germany</t>
+          <t>Rheinland-Pfalz, Germany</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29746,126 +29676,52 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
         </is>
       </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:DE-BW:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL151" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>0</v>
-      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
         <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -29937,12 +29793,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>DE-RP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Rheinland-Pfalz, Germany</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -29976,10 +29832,10 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -30023,12 +29879,12 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>country:DE-BY:national</t>
+          <t>country:DE-RP:national</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
         <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AE152" t="inlineStr">
@@ -30072,30 +29928,34 @@
         </is>
       </c>
       <c r="AN152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
         <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -30162,17 +30022,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>DE-HB</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bremen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -30197,175 +30057,98 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>2</v>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:DE-HB:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL153" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30392,17 +30175,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -30427,175 +30210,98 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL154" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30622,17 +30328,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>DE-HH</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hamburg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -30657,2702 +30363,96 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>2</v>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:DE-HH:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL155" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>DE-MV</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Mecklenburg-Vorpommern, Germany</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N156" t="n">
-        <v>2</v>
-      </c>
-      <c r="O156" t="n">
-        <v>2</v>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:DE-MV:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL156" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
-      <c r="AT156" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV156" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW156" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX156" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ156" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA156" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB156" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC156" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>DE-NI</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>Niedersachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N157" t="n">
-        <v>2</v>
-      </c>
-      <c r="O157" t="n">
-        <v>2</v>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:DE-NI:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
-      <c r="AT157" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV157" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW157" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX157" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ157" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA157" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB157" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC157" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>DE-NW</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Nordrhein-Westfalen, Germany</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N158" t="n">
-        <v>2</v>
-      </c>
-      <c r="O158" t="n">
-        <v>2</v>
-      </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:DE-NW:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL158" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
-      <c r="AT158" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV158" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW158" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX158" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ158" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA158" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB158" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC158" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>DE-RP</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Rheinland-Pfalz, Germany</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N159" t="n">
-        <v>2</v>
-      </c>
-      <c r="O159" t="n">
-        <v>2</v>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:DE-RP:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL159" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
-      <c r="AT159" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV159" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW159" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX159" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ159" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA159" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB159" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC159" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>DE-SH</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Schleswig-Holstein, Germany</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N160" t="n">
-        <v>2</v>
-      </c>
-      <c r="O160" t="n">
-        <v>2</v>
-      </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:DE-SH:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL160" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
-      <c r="AT160" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV160" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW160" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX160" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ160" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA160" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB160" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC160" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>DE-SL</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Saarland, Germany</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N161" t="n">
-        <v>2</v>
-      </c>
-      <c r="O161" t="n">
-        <v>2</v>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:DE-SL:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL161" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
-      <c r="AT161" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV161" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW161" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX161" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ161" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA161" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB161" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC161" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N162" t="n">
-        <v>2</v>
-      </c>
-      <c r="O162" t="n">
-        <v>2</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:DE-SN:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
-      <c r="AT162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV162" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW162" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX162" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ162" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA162" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB162" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC162" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>DE-ST</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Sachsen-Anhalt, Germany</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N163" t="n">
-        <v>2</v>
-      </c>
-      <c r="O163" t="n">
-        <v>2</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:DE-ST:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
-      <c r="AT163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW163" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX163" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ163" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA163" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB163" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC163" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>DE-TH</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Thüringen, Germany</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>2009-09</t>
-        </is>
-      </c>
-      <c r="N164" t="n">
-        <v>2</v>
-      </c>
-      <c r="O164" t="n">
-        <v>2</v>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>virale-h-morrhagische-fieber</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Virale hämorrhagische Fieber</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:DE-TH:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
-        <is>
-          <t>sha256:cdf366a6099bea21da164996d9f05447e9db19ab28be2dc25988a487e5ebcdc7</t>
-        </is>
-      </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
-      <c r="AT164" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
-      <c r="AV164" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW164" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX164" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ164" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA164" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB164" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC164" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>2009-10-01</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>2009-10</t>
-        </is>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP165" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr"/>
-      <c r="AT165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV165" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW165" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX165" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ165" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA165" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB165" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC165" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>2009-11-01</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="N166" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP166" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
-      <c r="AT166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV166" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW166" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX166" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ166" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA166" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB166" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC166" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
-      <c r="AT167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV167" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW167" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX167" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ167" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA167" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB167" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC167" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -33474,7 +30574,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -33484,7 +30584,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -33504,7 +30604,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -33536,7 +30636,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -6804,11 +6804,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
@@ -6826,12 +6821,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ41" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -6841,11 +6831,6 @@
       </c>
       <c r="AT41" t="n">
         <v>1</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6911,17 +6896,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6960,34 +6945,12 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Other Viral Haemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6995,64 +6958,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN42" t="b">
-        <v>1</v>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7060,27 +6965,17 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT42" t="n">
         <v>1</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -7088,7 +6983,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -7108,7 +7003,7 @@
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
@@ -7150,12 +7045,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7180,12 +7075,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7194,22 +7089,20 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
@@ -7217,52 +7110,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7213,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7462,12 +7351,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7600,12 +7489,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7738,12 +7627,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7876,12 +7765,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7984,12 +7873,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8014,12 +7903,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8028,20 +7917,22 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_AT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -8049,48 +7940,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_AT_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ages_radar</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Austria AGES Radar for Infectious Diseases</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_monthly_csv</t>
         </is>
       </c>
     </row>
@@ -8122,12 +8017,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8171,7 +8066,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_BE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -8191,7 +8086,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_AT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_BE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -8199,42 +8094,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>ages_radar</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Austria AGES Radar for Infectious Diseases</t>
+          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.ages.at/en/human/disease/ages-radar-for-infectious-diseases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>official_monthly_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8161,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8313,9 +8208,14 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -8330,55 +8230,65 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_BE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
       <c r="AT51" t="n">
         <v>1</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Belgium Annual Baseline</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8315,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8454,23 +8364,98 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Viral Haemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -8564,17 +8549,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8613,34 +8598,12 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>SRC_CA_PHAC_CNDSS</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Viral Haemorrhagic Fever</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>provincial_territorial_voluntary_notifications_national</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -8648,64 +8611,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>country:CA:national</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN53" t="b">
-        <v>1</v>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -8713,65 +8618,55 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_CA_PHAC_CNDSS_D141_ANNUAL</t>
+          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT53" t="n">
         <v>1</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Canada PHAC CNDSS Annual</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -8803,12 +8698,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8852,7 +8747,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_DE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8872,7 +8767,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_DE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -8880,42 +8775,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8842,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8996,7 +8891,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_DK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -9016,7 +8911,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_DE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_DK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -9024,42 +8919,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9091,12 +8986,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9140,7 +9035,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_EE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -9160,7 +9055,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_DK_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_EE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -9173,7 +9068,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -9193,7 +9088,7 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Denmark Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
@@ -9235,12 +9130,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9284,7 +9179,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -9304,7 +9199,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -9317,7 +9212,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -9337,7 +9232,7 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
@@ -9379,12 +9274,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9428,7 +9323,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_FI_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -9448,7 +9343,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_FI_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -9456,42 +9351,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9523,12 +9418,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9572,7 +9467,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -9592,7 +9487,7 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -9600,42 +9495,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9562,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9716,7 +9611,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_GB_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -9736,7 +9631,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_GB_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -9749,7 +9644,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -9769,7 +9664,7 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
@@ -9811,12 +9706,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9860,7 +9755,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9880,7 +9775,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -9893,7 +9788,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -9913,7 +9808,7 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
@@ -9955,12 +9850,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9999,22 +9894,20 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
@@ -10022,52 +9915,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_GR_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Greece Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10099,12 +9988,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10143,20 +10032,22 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
@@ -10164,48 +10055,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_VHFOTH_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10237,12 +10132,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10286,7 +10181,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -10306,7 +10201,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -10314,42 +10209,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10276,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10430,7 +10325,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -10450,7 +10345,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_IS_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -10458,42 +10353,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -10525,12 +10420,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10574,7 +10469,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -10594,7 +10489,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_IT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -10607,7 +10502,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -10627,7 +10522,7 @@
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Italy Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
@@ -10669,12 +10564,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10718,7 +10613,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -10738,7 +10633,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -10751,7 +10646,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -10771,7 +10666,7 @@
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
@@ -10813,12 +10708,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10862,7 +10757,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LV_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10882,7 +10777,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_LV_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -10895,7 +10790,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -10915,7 +10810,7 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
@@ -10957,12 +10852,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11006,7 +10901,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_MT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -11026,7 +10921,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_MT_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -11039,7 +10934,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -11059,7 +10954,7 @@
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
@@ -11101,12 +10996,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11150,7 +11045,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_NL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -11170,7 +11065,7 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_NL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -11183,7 +11078,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -11203,7 +11098,7 @@
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
@@ -11245,12 +11140,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11294,7 +11189,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_NO_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -11314,7 +11209,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_NL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_NO_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -11322,42 +11217,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11389,12 +11284,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11438,7 +11333,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -11458,7 +11353,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_NO_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT72" t="n">
@@ -11466,42 +11361,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11533,12 +11428,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11582,7 +11477,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -11602,7 +11497,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -11615,7 +11510,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -11635,7 +11530,7 @@
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
@@ -11677,12 +11572,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11726,7 +11621,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -11746,7 +11641,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SE_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -11754,42 +11649,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11821,12 +11716,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11870,7 +11765,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11890,7 +11785,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_SE_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -11898,42 +11793,42 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -11965,12 +11860,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -12012,14 +11907,9 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -12034,27 +11924,17 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
+          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
         </is>
       </c>
       <c r="AT76" t="n">
         <v>1</v>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -12062,7 +11942,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -12082,7 +11962,7 @@
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
@@ -12119,17 +11999,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12154,12 +12034,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12168,165 +12048,69 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Other Viral Haemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
-        </is>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12358,12 +12142,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12388,12 +12172,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12402,22 +12186,20 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
@@ -12425,52 +12207,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_SK_ECDC_VHFOTH_ANNUAL</t>
-        </is>
-      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12532,12 +12310,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12670,12 +12448,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12808,12 +12586,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12946,12 +12724,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -13084,12 +12862,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13222,12 +13000,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-09-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13330,12 +13108,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-BW</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13360,34 +13138,33 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
@@ -13395,48 +13172,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS85" t="inlineStr"/>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13468,12 +13249,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>DE-RP</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Rheinland-Pfalz, Germany</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13498,7 +13279,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13507,25 +13288,24 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
@@ -13533,48 +13313,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS86" t="inlineStr"/>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13606,12 +13390,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DE-BW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Baden-Württemberg, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13636,33 +13420,34 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
@@ -13670,52 +13455,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
+      <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13528,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DE-RP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz, Germany</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13777,33 +13558,34 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
@@ -13811,52 +13593,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>HOLD_DE_41c62070fa27cfedfd91bec027ba</t>
-        </is>
-      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13918,12 +13696,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-12-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -13993,282 +13771,6 @@
         </is>
       </c>
       <c r="BC89" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>2009-11-01</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
-      <c r="AT90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV90" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA90" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB90" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC90" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>viral-hemorrhagic-fevers</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>D127</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Viral hemorrhagic fevers</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>病毒性出血热</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>2009-12-01</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP91" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
-      <c r="AT91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV91" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>chp_notifiable</t>
-        </is>
-      </c>
-      <c r="BA91" t="inlineStr">
-        <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
-        </is>
-      </c>
-      <c r="BB91" t="inlineStr">
-        <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
-        </is>
-      </c>
-      <c r="BC91" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -14400,7 +13902,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -14420,7 +13922,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -14430,7 +13932,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d127/2005-2009.xlsx
+++ b/diseases/d127/2005-2009.xlsx
@@ -16288,6 +16288,11 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16300,12 +16305,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -16426,6 +16441,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16438,12 +16458,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -16564,6 +16594,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16576,12 +16611,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -16702,6 +16747,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16714,12 +16764,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -16840,6 +16900,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16852,12 +16917,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -16978,6 +17053,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16990,12 +17070,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -21832,6 +21922,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21844,12 +21939,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -27731,6 +27836,11 @@
       <c r="R140" t="n">
         <v>0</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27743,12 +27853,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -27869,6 +27989,11 @@
       <c r="R141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27881,12 +28006,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -28007,6 +28142,11 @@
       <c r="R142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28019,12 +28159,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -28145,6 +28295,11 @@
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28157,12 +28312,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -28283,6 +28448,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28295,12 +28465,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -28421,6 +28601,11 @@
       <c r="R145" t="n">
         <v>0</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28433,12 +28618,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -28559,6 +28754,11 @@
       <c r="R146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28571,12 +28771,22 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -28697,6 +28907,11 @@
       <c r="R147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28709,12 +28924,22 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -29852,6 +30077,11 @@
       <c r="R153" t="n">
         <v>0</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29864,12 +30094,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -29990,6 +30230,11 @@
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30002,12 +30247,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -30128,6 +30383,11 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30140,12 +30400,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
